--- a/whoscored/injuries.xlsx
+++ b/whoscored/injuries.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Piero Hincapie</t>
+          <t>Bukayo Saka</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>William Saliba</t>
+          <t>Piero Hincapie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -507,12 +507,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Low back</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
@@ -524,49 +524,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Christos Tzolis</t>
+          <t>William Saliba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Low back</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Modou Keba Cisse</t>
+          <t>Christos Tzolis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Johan Manzambi</t>
+          <t>Modou Keba Cisse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Matteo Ruggeri</t>
+          <t>Johan Manzambi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amadou Onana</t>
+          <t>Matteo Ruggeri</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -642,24 +642,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2027-06-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Veljko Milosavljevic</t>
+          <t>Amadou Onana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2027-06-01</t>
         </is>
       </c>
     </row>
@@ -686,22 +686,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eli Junior Kroupi</t>
+          <t>Veljko Milosavljevic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alex Scott</t>
+          <t>Eli Junior Kroupi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Julian Araujo</t>
+          <t>Alex Scott</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -755,34 +755,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yehor Yarmoliuk</t>
+          <t>Julian Araujo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vitaly Janelt</t>
+          <t>Yehor Yarmoliuk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2nd yellow (Red)</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-08</t>
         </is>
       </c>
     </row>
@@ -821,22 +821,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jannik Schuster</t>
+          <t>Vitaly Janelt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>2nd yellow (Red)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -848,22 +848,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Joshua Dasilva</t>
+          <t>Jannik Schuster</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Antoni Milambo</t>
+          <t>Joshua Dasilva</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -885,39 +885,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pascal Struijk</t>
+          <t>Antoni Milambo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zadok Yohanna</t>
+          <t>Pascal Struijk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yankuba Minteh</t>
+          <t>Zadok Yohanna</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -983,17 +983,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mats Wieffer</t>
+          <t>Yankuba Minteh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1010,22 +1010,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Femi Azeez</t>
+          <t>Mats Wieffer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1037,22 +1037,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kaoru Mitoma</t>
+          <t>Femi Azeez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1064,22 +1064,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Evan Ferguson</t>
+          <t>Kaoru Mitoma</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-08</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stefanos Tzimas</t>
+          <t>Evan Ferguson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1101,39 +1101,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Axel Disasi</t>
+          <t>Stefanos Tzimas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pep Chavarria</t>
+          <t>Axel Disasi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Malo Gusto</t>
+          <t>Pep Chavarria</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Illness</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Emiliano Martinez</t>
+          <t>Malo Gusto</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1226,22 +1226,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Emanuel Emegha</t>
+          <t>Emiliano Martinez</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Head</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-05</t>
         </is>
       </c>
     </row>
@@ -1253,22 +1253,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Reece James</t>
+          <t>Emanuel Emegha</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1280,22 +1280,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jamie Gittens</t>
+          <t>Reece James</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2027-01-03</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mykhaylo Mudryk</t>
+          <t>Jamie Gittens</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1329,27 +1329,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Luke Woolfenden</t>
+          <t>Mykhaylo Mudryk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1361,17 +1361,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Josh Eccles</t>
+          <t>Luke Woolfenden</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Haji Wright</t>
+          <t>Josh Eccles</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
@@ -1415,34 +1415,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aurele Amenda</t>
+          <t>Haji Wright</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ben Chilwell</t>
+          <t>Aurele Amenda</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-12-19</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4102,17 +4102,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>P. Hoejbjerg</t>
+          <t>Derek Cornelius</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4124,27 +4124,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Derek Cornelius</t>
+          <t>Paris Brunner</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paris Brunner</t>
+          <t>Stanis Idumbo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4183,17 +4183,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stanis Idumbo</t>
+          <t>Eric Dier</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4205,27 +4205,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eric Dier</t>
+          <t>Salis Abdul Samed</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4237,22 +4237,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Salis Abdul Samed</t>
+          <t>Ali Abdi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ali Abdi</t>
+          <t>Antoine Mendy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-05-29</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Antoine Mendy</t>
+          <t>Moise Bombito</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2027-05-29</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
@@ -4318,49 +4318,49 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Moise Bombito</t>
+          <t>Laurent Abergel</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2027-04-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Laurent Abergel</t>
+          <t>Ousmane Dembele</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2027-04-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4372,17 +4372,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ousmane Dembele</t>
+          <t>Marquinhos</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4399,17 +4399,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marquinhos</t>
+          <t>K. Kvaratskhelia</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4426,17 +4426,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>K. Kvaratskhelia</t>
+          <t>Alessandro Longoni</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4453,17 +4453,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alessandro Longoni</t>
+          <t>Nuno Mendes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nuno Mendes</t>
+          <t>Mamadou Mbow</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mamadou Mbow</t>
+          <t>Nhoa Sangui</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4534,22 +4534,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nhoa Sangui</t>
+          <t>Luca Koleosho</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Luca Koleosho</t>
+          <t>Jonathan Ikone</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4583,22 +4583,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jonathan Ikone</t>
+          <t>Brice Samba</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4615,17 +4615,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brice Samba</t>
+          <t>Esteban Lepaul</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4642,17 +4642,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Esteban Lepaul</t>
+          <t>Mikayil Faye</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4664,22 +4664,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mikayil Faye</t>
+          <t>Fabio Balde</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Illness</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4696,22 +4696,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fabio Balde</t>
+          <t>Hermann Diandaga</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4723,12 +4723,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hermann Diandaga</t>
+          <t>Deivid Washington</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deivid Washington</t>
+          <t>Maxi Oyedele</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Maxi Oyedele</t>
+          <t>Sebastian Nanasi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sebastian Nanasi</t>
+          <t>Ismael Doukoure</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ismael Doukoure</t>
+          <t>Martial Godo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Martial Godo</t>
+          <t>Joaquin Panichelli</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4868,39 +4868,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-12-05</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Joaquin Panichelli</t>
+          <t>Aron Doennum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>2nd yellow (Red)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4912,17 +4912,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aron Doennum</t>
+          <t>Sion Oppong</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2nd yellow (Red)</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4939,49 +4939,49 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sion Oppong</t>
+          <t>Abu Francis</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Abu Francis</t>
+          <t>Paolo Gozzi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Paolo Gozzi</t>
+          <t>Ismael Boura</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5003,37 +5003,10 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Troyes</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Ismael Boura</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Defender</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Hip</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5050,7 +5023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5466,17 +5439,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Joshua Kimmich</t>
+          <t>Luis Diaz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Personal reason</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5493,17 +5466,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jamal Musiala</t>
+          <t>Joshua Kimmich</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Personal reason</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5520,17 +5493,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tarek Buchmann</t>
+          <t>Jamal Musiala</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5542,22 +5515,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>K. Karetsas</t>
+          <t>Tarek Buchmann</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5574,7 +5547,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>G. Konstantelias</t>
+          <t>K. Karetsas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5584,12 +5557,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2027-06-01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5574,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Emre Can</t>
+          <t>G. Konstantelias</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5616,7 +5589,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-06-01</t>
         </is>
       </c>
     </row>
@@ -5628,34 +5601,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Justin Lerma</t>
+          <t>Emre Can</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tom Zimmerschied</t>
+          <t>Justin Lerma</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5665,7 +5638,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5682,17 +5655,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Felix Keidel</t>
+          <t>Tom Zimmerschied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5709,17 +5682,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cole Campbell</t>
+          <t>Felix Keidel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5736,7 +5709,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Francis Onyeka</t>
+          <t>Cole Campbell</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5746,7 +5719,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5763,12 +5736,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luis Seifert</t>
+          <t>Francis Onyeka</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5785,12 +5758,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FC Koln</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Joel Schmied</t>
+          <t>Luis Seifert</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5800,7 +5773,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5817,7 +5790,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rav van den Berg</t>
+          <t>Joel Schmied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5827,7 +5800,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5844,12 +5817,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ellyes Skhiri</t>
+          <t>Rav van den Berg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5871,17 +5844,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ragnar Ache</t>
+          <t>Ellyes Skhiri</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5898,17 +5871,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timo Huebers</t>
+          <t>Ragnar Ache</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5920,22 +5893,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Frankfurt</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oscar Hoejlund</t>
+          <t>Timo Huebers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5952,7 +5925,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hugo Larsson</t>
+          <t>Oscar Hoejlund</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5962,12 +5935,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5979,22 +5952,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nnamdi Collins</t>
+          <t>Hugo Larsson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6006,17 +5979,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jessic Ngankam</t>
+          <t>Nnamdi Collins</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6033,7 +6006,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Malik Pimpong</t>
+          <t>Jessic Ngankam</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6043,7 +6016,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Knock</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6055,12 +6028,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Frankfurt</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yuito Suzuki</t>
+          <t>Malik Pimpong</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6070,12 +6043,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2nd yellow (Red)</t>
+          <t>Knock</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6087,22 +6060,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Berkay Yilmaz</t>
+          <t>Yuito Suzuki</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Knock</t>
+          <t>2nd yellow (Red)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6087,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bruno Ogbus</t>
+          <t>Berkay Yilmaz</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6124,7 +6097,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knock</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -6141,34 +6114,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Florent Muslija</t>
+          <t>Bruno Ogbus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fabio Vieira</t>
+          <t>Florent Muslija</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6178,12 +6151,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-01-15</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6168,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Albert Sambi Lokonga</t>
+          <t>Fabio Vieira</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6205,7 +6178,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6222,17 +6195,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bakery Jatta</t>
+          <t>Albert Sambi Lokonga</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6249,17 +6222,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nicolai Remberg</t>
+          <t>Bakery Jatta</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6276,17 +6249,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Patson Daka</t>
+          <t>Nicolai Remberg</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6303,17 +6276,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fernando Dickes</t>
+          <t>Patson Daka</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Shoulder</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6325,27 +6298,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Fernando Dickes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2nd yellow (Red)</t>
+          <t>Shoulder</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6357,22 +6330,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nathan De Cat</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>2nd yellow (Red)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6357,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Patrick Wimmer</t>
+          <t>Nathan De Cat</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6394,7 +6367,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6411,17 +6384,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Albian Hajdari</t>
+          <t>Patrick Wimmer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6433,22 +6406,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Martin Terrier</t>
+          <t>Albian Hajdari</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6465,7 +6438,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Montrell Culbreath</t>
+          <t>Martin Terrier</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6475,12 +6448,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6465,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eliesse Ben Seghir</t>
+          <t>Montrell Culbreath</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6502,12 +6475,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6492,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Christian Kofane</t>
+          <t>Eliesse Ben Seghir</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6529,7 +6502,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6546,17 +6519,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Noah Mbamba</t>
+          <t>Christian Kofane</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6573,17 +6546,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Guela Doue</t>
+          <t>Noah Mbamba</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6600,17 +6573,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kennet Eichhorn</t>
+          <t>Guela Doue</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Illness</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6622,12 +6595,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Otto Ruoppi</t>
+          <t>Kennet Eichhorn</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6637,7 +6610,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6654,7 +6627,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dominik Kohr</t>
+          <t>Otto Ruoppi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6664,12 +6637,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6681,22 +6654,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Robin Zentner</t>
+          <t>Dominik Kohr</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -6708,17 +6681,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Silas Katompa Mvumpa</t>
+          <t>Robin Zentner</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6730,27 +6703,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timur Gayret</t>
+          <t>Silas Katompa Mvumpa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6735,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>N. Awortwie-Grant</t>
+          <t>Timur Gayret</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6789,22 +6762,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mattes Hansen</t>
+          <t>N. Awortwie-Grant</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6816,17 +6789,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Marcel Hoffmeier</t>
+          <t>Mattes Hansen</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6843,17 +6816,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sebastian Klaas</t>
+          <t>Marcel Hoffmeier</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6870,17 +6843,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lasse Eickel</t>
+          <t>Sebastian Klaas</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Low back</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6892,22 +6865,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lukas Klostermann</t>
+          <t>Lasse Eickel</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Low back</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6924,22 +6897,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>F. Assan Ouedraogo</t>
+          <t>Lukas Klostermann</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Shoulder</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6951,22 +6924,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Marc Guiu</t>
+          <t>F. Assan Ouedraogo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Shoulder</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-12-25</t>
         </is>
       </c>
     </row>
@@ -6978,17 +6951,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Viggo Gebel</t>
+          <t>Marc Guiu</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7005,7 +6978,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C. Baumgartner</t>
+          <t>Viggo Gebel</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7015,39 +6988,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Edin Dzeko</t>
+          <t>C. Baumgartner</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -7059,17 +7032,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Adil Aouchiche</t>
+          <t>Edin Dzeko</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Head</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7086,22 +7059,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bryan Lasme</t>
+          <t>Adil Aouchiche</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wrist</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7113,22 +7086,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Johannes Siebeking</t>
+          <t>Bryan Lasme</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Wrist</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -7140,17 +7113,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Moussa Sylla</t>
+          <t>Johannes Siebeking</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7167,17 +7140,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dejan Ljubicic</t>
+          <t>Moussa Sylla</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7189,22 +7162,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Josha Vagnoman</t>
+          <t>Dejan Ljubicic</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7221,17 +7194,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Noah Darvich</t>
+          <t>Josha Vagnoman</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7248,22 +7221,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dan-Axel Zagadou</t>
+          <t>Noah Darvich</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7275,17 +7248,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Justin Diehl</t>
+          <t>Dan-Axel Zagadou</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7302,7 +7275,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tiago Tomas</t>
+          <t>Justin Diehl</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7317,7 +7290,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7302,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jeremy Arevalo</t>
+          <t>Tiago Tomas</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7339,7 +7312,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Upper back</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7351,22 +7324,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Derrick Koehn</t>
+          <t>Jeremy Arevalo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Upper back</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7383,17 +7356,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Livan Burcu</t>
+          <t>Derrick Koehn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Illness</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7410,22 +7383,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stanley N'Soki</t>
+          <t>Livan Burcu</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7410,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Marvin Friedrich</t>
+          <t>Stanley N'Soki</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7447,12 +7420,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Knock</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7437,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Andrik Markgraf</t>
+          <t>Marvin Friedrich</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7474,12 +7447,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Knock</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2027-04-02</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7491,22 +7464,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Josip Juranovic</t>
+          <t>Andrik Markgraf</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Illness</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-04-02</t>
         </is>
       </c>
     </row>
@@ -7518,12 +7491,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Andrej Ilic</t>
+          <t>Josip Juranovic</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7540,22 +7513,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Skelly Alvero</t>
+          <t>Andrej Ilic</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7572,17 +7545,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Salim Musah</t>
+          <t>Skelly Alvero</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7599,7 +7572,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Keke Topp</t>
+          <t>Salim Musah</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7609,12 +7582,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7626,22 +7599,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Senne Lynen</t>
+          <t>Keke Topp</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-02-05</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7626,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Justin Njinmah</t>
+          <t>Senne Lynen</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7663,12 +7636,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7653,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jens Stage</t>
+          <t>Justin Njinmah</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7695,7 +7668,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -7707,20 +7680,47 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>Jens Stage</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Midfielder</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Thigh</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>Felix Agu</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Defender</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7737,7 +7737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7775,22 +7775,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Angel Perez</t>
+          <t>Facundo Garces</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2027-01-05</t>
         </is>
       </c>
     </row>
@@ -7802,12 +7802,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Facundo Garces</t>
+          <t>Mikel Rodriguez</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-04-04</t>
         </is>
       </c>
     </row>
@@ -7829,34 +7829,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mikel Rodriguez</t>
+          <t>Facundo Garces</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2027-04-04</t>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Facundo Garces</t>
+          <t>Aymeric Laporte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pablo Duran</t>
+          <t>Borja Iglesias</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8261,17 +8261,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Borja Iglesias</t>
+          <t>Carl Starfelt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carl Starfelt</t>
+          <t>Miguel Roman</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Miguel Roman</t>
+          <t>Jones El-Abdellaoui</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8337,12 +8337,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jones El-Abdellaoui</t>
+          <t>Lorenzo Amatucci</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lorenzo Amatucci</t>
+          <t>Yeremay Hernandez</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Head</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8396,17 +8396,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yeremay Hernandez</t>
+          <t>Bright Ede</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bright Ede</t>
+          <t>Noe Carrillo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -8450,17 +8450,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Noe Carrillo</t>
+          <t>P. Aubameyang</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -8477,17 +8477,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>P. Aubameyang</t>
+          <t>Zakaria Eddahchouri</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Wrist</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8499,12 +8499,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zakaria Eddahchouri</t>
+          <t>Marc Aguado</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wrist</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -8531,22 +8531,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marc Aguado</t>
+          <t>Adam Boayar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -8558,34 +8558,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adam Boayar</t>
+          <t>Yago Santiago</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yago Santiago</t>
+          <t>Pol Lozano</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -8612,22 +8612,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pol Lozano</t>
+          <t>Jofre Carreras</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Physical discom</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jofre Carreras</t>
+          <t>Kike Garcia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8649,39 +8649,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Physical discom</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2027-01-15</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kike Garcia</t>
+          <t>Djene</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
@@ -8693,22 +8693,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Djene</t>
+          <t>Martin Satriano</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8747,17 +8747,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Martin Satriano</t>
+          <t>Zaid Abner Romero</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -8774,22 +8774,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zaid Abner Romero</t>
+          <t>Juanmi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
@@ -8801,49 +8801,49 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Juanmi</t>
+          <t>Christantus Uche</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2027-06-12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Christantus Uche</t>
+          <t>Diego Murillo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2027-06-12</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -8855,22 +8855,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Diego Murillo</t>
+          <t>Julen Lobete</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2027-06-30</t>
         </is>
       </c>
     </row>
@@ -8882,34 +8882,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Julen Lobete</t>
+          <t>Aaron Ochoa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aaron Ochoa</t>
+          <t>Iker Munoz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Iker Munoz</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -8963,17 +8963,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Jorge Herrando</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -8990,76 +8990,76 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jorge Herrando</t>
+          <t>Romain Del Castillo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Romain Del Castillo</t>
+          <t>Simon Eriksson</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Shoulder</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Simon Eriksson</t>
+          <t>Pathe Ciss</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Shoulder</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pathe Ciss</t>
+          <t>Unai Lopez</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9098,17 +9098,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Unai Lopez</t>
+          <t>Randy Nteka</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Low back</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -9125,17 +9125,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Randy Nteka</t>
+          <t>Luiz Felipe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Low back</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Luiz Felipe</t>
+          <t>Andrei Ratiu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -9179,49 +9179,49 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Andrei Ratiu</t>
+          <t>Augusto Batalla</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-01-09</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Augusto Batalla</t>
+          <t>Facundo Bernal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2026-11-29</t>
         </is>
       </c>
     </row>
@@ -9233,22 +9233,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Facundo Bernal</t>
+          <t>Juan Hernandez</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9260,17 +9260,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Juan Hernandez</t>
+          <t>Junior Firpo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -9287,17 +9287,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Junior Firpo</t>
+          <t>Aitor Ruibal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -9309,12 +9309,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Vinicius Junior</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-22</t>
         </is>
       </c>
     </row>
@@ -9341,22 +9341,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vinicius Junior</t>
+          <t>Ferland Mendy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Hip</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -9368,17 +9368,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ferland Mendy</t>
+          <t>Rodrygo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Hip</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -9395,49 +9395,49 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rodrygo</t>
+          <t>Raul Asencio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Raul Asencio</t>
+          <t>Pablo Marin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pablo Marin</t>
+          <t>Yangel Herrera</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9476,17 +9476,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yangel Herrera</t>
+          <t>Luken Beitia</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Luken Beitia</t>
+          <t>Jon Aramburu</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jon Aramburu</t>
+          <t>Alvaro Odriozola</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9540,39 +9540,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alvaro Odriozola</t>
+          <t>Isaac Romero</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>2nd yellow (Red)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2nd yellow (Red)</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9611,17 +9611,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Isaac Romero</t>
+          <t>Jon Guridi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jon Guridi</t>
+          <t>Giorgi Kochorashvili</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Giorgi Kochorashvili</t>
+          <t>Miguel Angel Sierra</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Miguel Angel Sierra</t>
+          <t>Marcao</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9714,12 +9714,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Marcao</t>
+          <t>Jose Copete</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9729,12 +9729,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jose Copete</t>
+          <t>Justin De Haas</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9773,22 +9773,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Justin De Haas</t>
+          <t>Diego Lopez</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-14</t>
         </is>
       </c>
     </row>
@@ -9800,22 +9800,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Diego Lopez</t>
+          <t>Dimitri Foulquier</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Physical discom</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9827,22 +9827,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dimitri Foulquier</t>
+          <t>Umar Sadiq</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Physical discom</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-07</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Umar Sadiq</t>
+          <t>Sergi Canos</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9864,24 +9864,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2027-01-01</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sergi Canos</t>
+          <t>Nicolas Pepe</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9891,37 +9891,10 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Nicolas Pepe</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Forward</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9938,7 +9911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10516,12 +10489,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ivan Azon</t>
+          <t>Trevoh Chalobah</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10543,12 +10516,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trevoh Chalobah</t>
+          <t>Assane Diao</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10570,7 +10543,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Assane Diao</t>
+          <t>Nicolas-Gerrit Kuehn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10580,7 +10553,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10592,22 +10565,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nicolas-Gerrit Kuehn</t>
+          <t>Luca Ranieri</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10634,7 +10607,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10651,7 +10624,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luca Ranieri</t>
+          <t>Niccolo Fortini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10661,12 +10634,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -10678,17 +10651,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Niccolo Fortini</t>
+          <t>Riccardo Sottil</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Low back</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -10705,7 +10678,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Riccardo Sottil</t>
+          <t>Roberto Piccoli</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -10715,12 +10688,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Low back</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10732,17 +10705,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Roberto Piccoli</t>
+          <t>Arthur Atta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Abdomen</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -10759,17 +10732,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Arthur Atta</t>
+          <t>Albert Gudmundsson</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Abdomen</t>
+          <t>Shoulder</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -10786,71 +10759,71 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Albert Gudmundsson</t>
+          <t>Fabiano Parisi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Shoulder</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fabiano Parisi</t>
+          <t>Florian Grillitsch</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Florian Grillitsch</t>
+          <t>Vitinha</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10867,22 +10840,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vitinha</t>
+          <t>Elias Havel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10867,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Elias Havel</t>
+          <t>Djibril Sow</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -10909,7 +10882,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10921,22 +10894,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Djibril Sow</t>
+          <t>Lorenzo Colombo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -10948,22 +10921,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lorenzo Colombo</t>
+          <t>Franz-Ethan Meichtry</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10975,22 +10948,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Franz-Ethan Meichtry</t>
+          <t>Joi Xheto Nuredini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
@@ -11002,7 +10975,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Joi Xheto Nuredini</t>
+          <t>Lorenzo Venturino</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11012,34 +10985,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lorenzo Venturino</t>
+          <t>Benjamin Pavard</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -11056,22 +11029,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Benjamin Pavard</t>
+          <t>Curtis Jones</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Groin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -11083,22 +11056,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Curtis Jones</t>
+          <t>Lautaro Martinez</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Groin</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-20</t>
         </is>
       </c>
     </row>
@@ -11110,22 +11083,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lautaro Martinez</t>
+          <t>Valentin Carboni</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11137,17 +11110,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Valentin Carboni</t>
+          <t>John Stones</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -11159,12 +11132,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>John Stones</t>
+          <t>Gleison Bremer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -11174,7 +11147,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -11191,17 +11164,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gleison Bremer</t>
+          <t>Chico Conceicao</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Shoulder</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -11218,22 +11191,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chico Conceicao</t>
+          <t>Augusto Owusu</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Shoulder</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -11245,22 +11218,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Augusto Owusu</t>
+          <t>Jeff Ekhator</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11245,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jeff Ekhator</t>
+          <t>Kenan Yildiz</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -11282,12 +11255,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-29</t>
         </is>
       </c>
     </row>
@@ -11299,22 +11272,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kenan Yildiz</t>
+          <t>Manuel Locatelli</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2027-02-06</t>
         </is>
       </c>
     </row>
@@ -11326,22 +11299,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Manuel Locatelli</t>
+          <t>Arkadiusz Milik</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11353,34 +11326,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Arkadiusz Milik</t>
+          <t>K. Thuram-Ulien</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-01-15</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>K. Thuram-Ulien</t>
+          <t>Nicolo Rovella</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -11390,12 +11363,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11380,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nicolo Rovella</t>
+          <t>Kenneth Taylor</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -11417,7 +11390,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -11434,12 +11407,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kenneth Taylor</t>
+          <t>Nuno Tavares</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11461,17 +11434,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nuno Tavares</t>
+          <t>Kenneth Taylor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -11488,7 +11461,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kenneth Taylor</t>
+          <t>Adam Marusic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -11498,7 +11471,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -11515,7 +11488,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adam Marusic</t>
+          <t>Nicolo Rovella</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11525,7 +11498,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -11542,17 +11515,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nicolo Rovella</t>
+          <t>Matteo Cancellieri</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11569,17 +11542,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Matteo Cancellieri</t>
+          <t>Alessio Furlanetto</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11591,22 +11564,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Alessio Furlanetto</t>
+          <t>Lassana Coulibaly</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -11623,7 +11596,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lassana Coulibaly</t>
+          <t>Medon Berisha</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -11645,22 +11618,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Medon Berisha</t>
+          <t>Exequiel Zeballos</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -11677,22 +11650,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lorenzo Lucchesi</t>
+          <t>Idrissa Toure</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11704,12 +11677,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Exequiel Zeballos</t>
+          <t>Matteo Pessina</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11719,46 +11692,46 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Idrissa Toure</t>
+          <t>David Neres</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Matteo Pessina</t>
+          <t>Antonio Vergara</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11768,12 +11741,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
@@ -11785,61 +11758,61 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>David Neres</t>
+          <t>A. Buongiorno</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Antonio Vergara</t>
+          <t>Lautaro Valenti</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A. Buongiorno</t>
+          <t>Lautaro Valenti</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11849,12 +11822,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Banned by club</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11866,22 +11839,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lautaro Valenti</t>
+          <t>Nesta Elphege</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Illness</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11893,17 +11866,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lautaro Valenti</t>
+          <t>Pontus Almqvist</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Banned by club</t>
+          <t>Calf</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -11920,17 +11893,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nesta Elphege</t>
+          <t>H. N. Caviglia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Illness</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -11942,12 +11915,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pontus Almqvist</t>
+          <t>Donyell Malen</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11957,34 +11930,34 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Calf</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>H. N. Caviglia</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Red card (direct)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -12001,22 +11974,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Donyell Malen</t>
+          <t>Lorenzo Pellegrini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12028,17 +12001,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Robinio Vaz</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Red card (direct)</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -12055,22 +12028,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lorenzo Pellegrini</t>
+          <t>Mile Svilar</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-21</t>
         </is>
       </c>
     </row>
@@ -12082,17 +12055,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Robinio Vaz</t>
+          <t>Manu Kone</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Muscle</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12109,12 +12082,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mile Svilar</t>
+          <t>Jan Ziolkowski</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -12124,19 +12097,19 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Manu Kone</t>
+          <t>Jay Idzes</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12146,7 +12119,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -12158,27 +12131,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jan Ziolkowski</t>
+          <t>Jay Idzes</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12190,17 +12163,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jay Idzes</t>
+          <t>Yeferson Paz</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Cruciate ligame</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12217,7 +12190,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jay Idzes</t>
+          <t>Daniel Boloca</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -12227,7 +12200,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -12244,34 +12217,34 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Yeferson Paz</t>
+          <t>Ismael Kone</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cruciate ligame</t>
+          <t>Lower leg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-01-03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Daniel Boloca</t>
+          <t>Emirhan Ilkhan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12281,7 +12254,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -12293,12 +12266,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ismael Kone</t>
+          <t>Ivan Ilic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12308,12 +12281,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Lower leg</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12325,17 +12298,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Emirhan Ilkhan</t>
+          <t>Franco Israel</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Goalkeeper</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Shoulder</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12347,12 +12320,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ivan Ilic</t>
+          <t>Hassane Kamara</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12362,7 +12335,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -12374,22 +12347,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Franco Israel</t>
+          <t>Sandi Lovric</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Goalkeeper</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Shoulder</t>
+          <t>Yellow cards</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -12406,12 +12379,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hassane Kamara</t>
+          <t>Thomas Kristensen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12433,22 +12406,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sandi Lovric</t>
+          <t>Vakoun Issouf Bayo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-13</t>
         </is>
       </c>
     </row>
@@ -12460,22 +12433,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Thomas Kristensen</t>
+          <t>Nicolo Zaniolo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Yellow cards</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12460,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vakoun Issouf Bayo</t>
+          <t>Idrissa Gueye</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -12497,66 +12470,66 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2027-01-03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nicolo Zaniolo</t>
+          <t>Marin Sverko</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Idrissa Gueye</t>
+          <t>Thierry Correia</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12568,17 +12541,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Marin Sverko</t>
+          <t>Andrea Adorante</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Low back</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -12595,22 +12568,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Thierry Correia</t>
+          <t>Gianluca Busio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Defender</t>
+          <t>Midfielder</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Thigh</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-11-23</t>
         </is>
       </c>
     </row>
@@ -12622,22 +12595,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Andrea Adorante</t>
+          <t>Bartol Franjic</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Low back</t>
+          <t>Shoulder</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-12-12</t>
         </is>
       </c>
     </row>
@@ -12649,74 +12622,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Gianluca Busio</t>
+          <t>Armel Bella-Kotchap</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Midfielder</t>
+          <t>Defender</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Thigh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Venezia</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Bartol Franjic</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Defender</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Shoulder</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>2026-12-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Venezia</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Armel Bella-Kotchap</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Defender</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
